--- a/artfynd/A 58515-2021 artfynd.xlsx
+++ b/artfynd/A 58515-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118095689</v>
+        <v>118097221</v>
       </c>
       <c r="B2" t="n">
-        <v>90784</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällbergsänge (Hällbergsänge), Hls</t>
+          <t>Hällänget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574887</v>
+        <v>574838</v>
       </c>
       <c r="R2" t="n">
-        <v>6789659</v>
+        <v>6789685</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,14 +752,24 @@
           <t>2024-06-29</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-29</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gammal granskog +100 år</t>
+          <t>Finns flera runt grov tall markeradvsom naturvård. Radie på 50 meter behövs.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,28 +778,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Inga-Greta Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Inga-Greta Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118097221</v>
+        <v>118095843</v>
       </c>
       <c r="B3" t="n">
-        <v>97838</v>
+        <v>90501</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,45 +809,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällänget, Hls</t>
+          <t>Hällbergsänge (Hällbergsänge), Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574838</v>
+        <v>574866</v>
       </c>
       <c r="R3" t="n">
-        <v>6789685</v>
+        <v>6789667</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,24 +870,9 @@
           <t>2024-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Finns flera runt grov tall markeradvsom naturvård. Radie på 50 meter behövs.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,124 +881,21 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inga-Greta Andersson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inga-Greta Andersson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>118095843</v>
-      </c>
-      <c r="B4" t="n">
-        <v>90501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Hällbergsänge (Hällbergsänge), Hls</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>574866</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6789667</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58515-2021 artfynd.xlsx
+++ b/artfynd/A 58515-2021 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>118095689</v>
       </c>
       <c r="B4" t="n">
-        <v>90788</v>
+        <v>90795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
